--- a/artfynd/A 32141-2021 artfynd.xlsx
+++ b/artfynd/A 32141-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123401296</v>
       </c>
       <c r="B2" t="n">
-        <v>57634</v>
+        <v>57640</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 32141-2021 artfynd.xlsx
+++ b/artfynd/A 32141-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123401296</v>
       </c>
       <c r="B2" t="n">
-        <v>57640</v>
+        <v>57643</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 32141-2021 artfynd.xlsx
+++ b/artfynd/A 32141-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123401296</v>
       </c>
       <c r="B2" t="n">
-        <v>57643</v>
+        <v>57644</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 32141-2021 artfynd.xlsx
+++ b/artfynd/A 32141-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>123401296</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32141-2021 artfynd.xlsx
+++ b/artfynd/A 32141-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123401296</v>
       </c>
       <c r="B2" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32141-2021 artfynd.xlsx
+++ b/artfynd/A 32141-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123401296</v>
       </c>
       <c r="B2" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32141-2021 artfynd.xlsx
+++ b/artfynd/A 32141-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123401296</v>
       </c>
       <c r="B2" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32141-2021 artfynd.xlsx
+++ b/artfynd/A 32141-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123401296</v>
       </c>
       <c r="B2" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32141-2021 artfynd.xlsx
+++ b/artfynd/A 32141-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123401296</v>
       </c>
       <c r="B2" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32141-2021 artfynd.xlsx
+++ b/artfynd/A 32141-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123401296</v>
       </c>
       <c r="B2" t="n">
-        <v>58063</v>
+        <v>58114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
